--- a/docs/downloads/经营分_津河省区__秦皇岛片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_津河省区__秦皇岛片区_2026-10-18.xlsx
@@ -1573,7 +1573,7 @@
         <v>77</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1658,14 +1658,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,提质量,附加分,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1693,7 +1693,7 @@
         <v>30</v>
       </c>
       <c r="S13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T13" t="n">
         <v>20</v>
@@ -2247,17 +2247,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6601186669309724675</t>
+          <t>6659401537346996238</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7天酒店秦皇岛东北大学秦皇小巷店</t>
+          <t>锦江之星秦皇岛昌黎酒店</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7天连锁酒店(秦皇岛东北大学珠江道店)</t>
+          <t>锦江之星(秦皇岛昌黎店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2269,7 +2269,7 @@
         <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2295,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2335,29 +2335,29 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6659401537346996238</t>
+          <t>7507807387181385765</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛昌黎酒店</t>
+          <t>维也纳酒店（秦皇岛北戴河老虎石店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛昌黎店)</t>
+          <t>维也纳酒店(秦皇岛市北戴河店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2371,13 +2371,13 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
+        <v>22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30</v>
+      </c>
+      <c r="O21" t="n">
         <v>25</v>
-      </c>
-      <c r="N21" t="n">
-        <v>30</v>
-      </c>
-      <c r="O21" t="n">
-        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
@@ -2423,17 +2423,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7507807387181385765</t>
+          <t>7369817645204146216</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳酒店（秦皇岛北戴河老虎石店）</t>
+          <t>非繁城品酒店·秦皇岛火车站万达世纪港湾店</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳酒店(秦皇岛市北戴河店)</t>
+          <t>非繁城品酒店(秦皇岛火车站万达世纪港湾店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2511,55 +2511,55 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7369817645204146216</t>
+          <t>7598771935769528354</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>非繁城品酒店·秦皇岛火车站万达世纪港湾店</t>
+          <t>锦江之星秦皇岛开发区高速口店</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>非繁城品酒店(秦皇岛火车站万达世纪港湾店)</t>
+          <t>锦江之星(秦皇岛开发区高速路口店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>搭门店,稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L23" t="n">
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2599,17 +2599,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7598771935769528354</t>
+          <t>6601186669309724675</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>锦江之星秦皇岛开发区高速口店</t>
+          <t>7天酒店秦皇岛东北大学秦皇小巷店</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛开发区高速路口店)</t>
+          <t>7天连锁酒店(秦皇岛东北大学珠江道店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2618,18 +2618,18 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>搭门店,稳房源,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L24" t="n">
         <v>10</v>
@@ -2775,33 +2775,33 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7369458680036591656</t>
+          <t>7555530999078062132</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛卢龙县酒店）</t>
+          <t>喆啡酒店（山海关火车站天下第一关古城店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>锦江之星酒店(秦皇岛卢龙店)</t>
+          <t>喆啡酒店(山海关火车站天下第一关古城店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>95</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2811,19 +2811,19 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2863,29 +2863,29 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7409962534867830824</t>
+          <t>7369458680036591656</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星（秦皇岛山海关火车站店）</t>
+          <t>锦江之星(秦皇岛卢龙县酒店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星(秦皇岛山海关火车站酒店)</t>
+          <t>锦江之星酒店(秦皇岛卢龙店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>95</v>
       </c>
       <c r="I27" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2899,13 +2899,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
+        <v>20</v>
+      </c>
+      <c r="N27" t="n">
+        <v>30</v>
+      </c>
+      <c r="O27" t="n">
         <v>25</v>
-      </c>
-      <c r="N27" t="n">
-        <v>30</v>
-      </c>
-      <c r="O27" t="n">
-        <v>20</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -2951,17 +2951,17 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7598010588934506522</t>
+          <t>7409962534867830824</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>麗枫酒店（北戴河火车站环境工程学院店）</t>
+          <t>锦江之星（秦皇岛山海关火车站店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>麗枫酒店(北戴河火车站环境工程学院店)</t>
+          <t>锦江之星(秦皇岛山海关火车站酒店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2970,24 +2970,24 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
@@ -3039,17 +3039,17 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7555530999078062132</t>
+          <t>7598010588934506522</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>喆啡酒店（山海关火车站天下第一关古城店）</t>
+          <t>麗枫酒店（北戴河火车站环境工程学院店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>喆啡酒店(山海关火车站天下第一关古城店)</t>
+          <t>麗枫酒店(北戴河火车站环境工程学院店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3058,18 +3058,18 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L29" t="n">
         <v>10</v>
@@ -3081,13 +3081,13 @@
         <v>30</v>
       </c>
       <c r="O29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P29" t="n">
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
